--- a/Constrained_BO/results/final_charging_opt_results/RW9/comparison_table.xlsx
+++ b/Constrained_BO/results/final_charging_opt_results/RW9/comparison_table.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CC ½C</t>
+          <t>CCCV ½C</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -507,13 +507,13 @@
         <v>80</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-138.33</v>
       </c>
       <c r="J2" t="n">
         <v>23.92</v>
@@ -528,7 +528,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>CC ½C</t>
+          <t>CCCV 2C</t>
         </is>
       </c>
     </row>
@@ -540,34 +540,44 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CC 1C</t>
+          <t>CCCV 1C</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13.32</v>
+        <v>55.73</v>
       </c>
       <c r="D3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="E3" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="F3" t="n">
+        <v>80.06</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-190.03</v>
+      </c>
       <c r="J3" t="n">
-        <v>25.26</v>
+        <v>24.19</v>
       </c>
       <c r="K3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>infeasible (energy target not met)</t>
+          <t>feasible</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>CC ½C</t>
+          <t>CCCV 2C</t>
         </is>
       </c>
     </row>
@@ -579,34 +589,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CC 2C</t>
+          <t>CCCV 2C</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.35</v>
+        <v>19.22</v>
       </c>
       <c r="D4" t="n">
-        <v>12.34</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="E4" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="F4" t="n">
+        <v>79.95999999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
       <c r="J4" t="n">
-        <v>29.55</v>
+        <v>24.75</v>
       </c>
       <c r="K4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>infeasible (energy target not met)</t>
+          <t>feasible</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>CC ½C</t>
+          <t>CCCV 2C</t>
         </is>
       </c>
     </row>
@@ -634,13 +654,13 @@
         <v>80.67</v>
       </c>
       <c r="G5" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="H5" t="n">
-        <v>4.02</v>
+        <v>3.71</v>
       </c>
       <c r="I5" t="n">
-        <v>29.51</v>
+        <v>-68</v>
       </c>
       <c r="J5" t="n">
         <v>24.77</v>
@@ -655,7 +675,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>CC ½C</t>
+          <t>CCCV 2C</t>
         </is>
       </c>
     </row>
@@ -683,13 +703,13 @@
         <v>80.91</v>
       </c>
       <c r="G6" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="H6" t="n">
-        <v>5.17</v>
+        <v>4.87</v>
       </c>
       <c r="I6" t="n">
-        <v>25.29</v>
+        <v>-78.06</v>
       </c>
       <c r="J6" t="n">
         <v>24.01</v>
@@ -704,7 +724,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>CC ½C</t>
+          <t>CCCV 2C</t>
         </is>
       </c>
     </row>
@@ -732,13 +752,13 @@
         <v>81.48999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="H7" t="n">
-        <v>8.17</v>
+        <v>7.87</v>
       </c>
       <c r="I7" t="n">
-        <v>6.37</v>
+        <v>-123.16</v>
       </c>
       <c r="J7" t="n">
         <v>24.16</v>
@@ -753,7 +773,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>CC ½C</t>
+          <t>CCCV 2C</t>
         </is>
       </c>
     </row>

--- a/Constrained_BO/results/final_charging_opt_results/RW9/comparison_table.xlsx
+++ b/Constrained_BO/results/final_charging_opt_results/RW9/comparison_table.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,13 +507,13 @@
         <v>80</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-138.33</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>23.92</v>
@@ -528,7 +528,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>CCCV 2C</t>
+          <t>CCCV ½C</t>
         </is>
       </c>
     </row>
@@ -556,13 +556,13 @@
         <v>80.06</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.01</v>
+        <v>0.31</v>
       </c>
       <c r="I3" t="n">
-        <v>-190.03</v>
+        <v>-21.69</v>
       </c>
       <c r="J3" t="n">
         <v>24.19</v>
@@ -577,7 +577,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>CCCV 2C</t>
+          <t>CCCV ½C</t>
         </is>
       </c>
     </row>
@@ -589,32 +589,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CCCV 2C</t>
+          <t>Random</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19.22</v>
+        <v>32.28</v>
       </c>
       <c r="D4" t="n">
-        <v>40</v>
+        <v>40.01</v>
       </c>
       <c r="E4" t="n">
-        <v>20.04</v>
+        <v>19.33</v>
       </c>
       <c r="F4" t="n">
-        <v>79.95999999999999</v>
+        <v>80.67</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>29.51</v>
       </c>
       <c r="J4" t="n">
-        <v>24.75</v>
+        <v>24.77</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>CCCV 2C</t>
+          <t>CCCV ½C</t>
         </is>
       </c>
     </row>
@@ -638,32 +638,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Random</t>
+          <t>GP-BO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32.28</v>
+        <v>34.22</v>
       </c>
       <c r="D5" t="n">
         <v>40.01</v>
       </c>
       <c r="E5" t="n">
-        <v>19.33</v>
+        <v>19.09</v>
       </c>
       <c r="F5" t="n">
-        <v>80.67</v>
+        <v>80.91</v>
       </c>
       <c r="G5" t="n">
-        <v>0.71</v>
+        <v>0.91</v>
       </c>
       <c r="H5" t="n">
-        <v>3.71</v>
+        <v>5.17</v>
       </c>
       <c r="I5" t="n">
-        <v>-68</v>
+        <v>25.29</v>
       </c>
       <c r="J5" t="n">
-        <v>24.77</v>
+        <v>24.01</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
@@ -675,7 +675,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>CCCV 2C</t>
+          <t>CCCV ½C</t>
         </is>
       </c>
     </row>
@@ -687,32 +687,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GP-BO</t>
+          <t>GP-BO (min Q)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34.22</v>
+        <v>42.88</v>
       </c>
       <c r="D6" t="n">
-        <v>40.01</v>
+        <v>40.02</v>
       </c>
       <c r="E6" t="n">
-        <v>19.09</v>
+        <v>18.51</v>
       </c>
       <c r="F6" t="n">
-        <v>80.91</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.95</v>
+        <v>1.49</v>
       </c>
       <c r="H6" t="n">
-        <v>4.87</v>
+        <v>8.17</v>
       </c>
       <c r="I6" t="n">
-        <v>-78.06</v>
+        <v>6.37</v>
       </c>
       <c r="J6" t="n">
-        <v>24.01</v>
+        <v>24.16</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
@@ -724,56 +724,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>CCCV 2C</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RW9</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>GP-BO (min Q)</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>42.88</v>
-      </c>
-      <c r="D7" t="n">
-        <v>40.02</v>
-      </c>
-      <c r="E7" t="n">
-        <v>18.51</v>
-      </c>
-      <c r="F7" t="n">
-        <v>81.48999999999999</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="H7" t="n">
-        <v>7.87</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-123.16</v>
-      </c>
-      <c r="J7" t="n">
-        <v>24.16</v>
-      </c>
-      <c r="K7" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>CCCV 2C</t>
+          <t>CCCV ½C</t>
         </is>
       </c>
     </row>
